--- a/Docs/设备寄存器地址/天车寄存器地址表.xlsx
+++ b/Docs/设备寄存器地址/天车寄存器地址表.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地址总表" sheetId="1" r:id="Rafd9d0282662470a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作时序" sheetId="2" r:id="R5620da448d404e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通信与接口" sheetId="3" r:id="R1c2f4daec0ef4594"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地址总表" sheetId="1" r:id="R33c9778b7c834e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作时序" sheetId="2" r:id="Ra1a3116d0bf741a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通信与接口" sheetId="3" r:id="R128db09dc1224b2b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1649,7 +1649,7 @@
         <x:v>充磁</x:v>
       </x:c>
       <x:c r="G48" s="9" t="str">
-        <x:v>手动前置；写2，200ms后写0，再FC01读X6一次。</x:v>
+        <x:v>手动前置；写2，1000ms后写0，再FC01读X6一次。</x:v>
       </x:c>
       <x:c r="H48" s="9" t="str">
         <x:v>MagnetOnAsync
@@ -1677,7 +1677,7 @@
         <x:v>放磁 / 退磁</x:v>
       </x:c>
       <x:c r="G49" s="9" t="str">
-        <x:v>手动前置；写2，200ms后写0，再FC01读X7一次。</x:v>
+        <x:v>手动前置；写2，1000ms后写0，再FC01读X7一次。</x:v>
       </x:c>
       <x:c r="H49" s="9" t="str">
         <x:v>MagnetOffAsync
@@ -1883,7 +1883,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc094d8e55fd144dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R916d64c79e3143bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1933,7 +1933,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="4" t="str">
-        <x:v>200ms脉冲与500ms运动触发均为正常完成路径；各动作成功判据按下表区分。</x:v>
+        <x:v>充退磁1000ms、其他常规动作200ms、运动触发500ms均为正常完成路径；各动作成功判据按下表区分。</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -2159,7 +2159,7 @@
         <x:v>手动前置；手动按钮不额外检查X11</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>D4510=2，等200ms，D4510=0。</x:v>
+        <x:v>D4510=2，等1000ms，D4510=0。</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
         <x:v>单次FC01读取X6（63494）。</x:v>
@@ -2179,7 +2179,7 @@
         <x:v>手动前置</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>D4511=2，等200ms，D4511=0。</x:v>
+        <x:v>D4511=2，等1000ms，D4511=0。</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
         <x:v>单次FC01读取X7（63495）。</x:v>
@@ -2494,7 +2494,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R665a37b1656149c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re73a555e4c7a41de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2740,7 +2740,7 @@
         <x:v>正常与异常路径</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>200ms脉冲描述正常路径；普通动作无运动方法相同的finally复位。运动方法finally尽力把参加轴D4520/21/22清0，清0不等于急停。</x:v>
+        <x:v>充退磁1000ms、其他常规动作200ms脉冲描述正常路径；普通动作无运动方法相同的finally复位。运动方法finally尽力把参加轴D4520/21/22清0，清0不等于急停。</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
         <x:v>PulseAsync / HomeAsync / MoveAsync</x:v>
@@ -2894,8 +2894,8 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaa010be1c274704"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b30fbb26a17417a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0839a4a7d30d40ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0467c83bd09a43d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Docs/设备寄存器地址/天车寄存器地址表.xlsx
+++ b/Docs/设备寄存器地址/天车寄存器地址表.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地址总表" sheetId="1" r:id="R33c9778b7c834e39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作时序" sheetId="2" r:id="Ra1a3116d0bf741a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通信与接口" sheetId="3" r:id="R128db09dc1224b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地址总表" sheetId="1" r:id="R74863d87ab4b422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作时序" sheetId="2" r:id="R5edaac139932411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通信与接口" sheetId="3" r:id="Rde8d9bfc2b67420d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1649,7 +1649,7 @@
         <x:v>充磁</x:v>
       </x:c>
       <x:c r="G48" s="9" t="str">
-        <x:v>手动前置；写2，1000ms后写0，再FC01读X6一次。</x:v>
+        <x:v>手动前置；写2→固定200ms→写0；按配置等待（默认1000ms），再单读X6一次。</x:v>
       </x:c>
       <x:c r="H48" s="9" t="str">
         <x:v>MagnetOnAsync
@@ -1677,7 +1677,7 @@
         <x:v>放磁 / 退磁</x:v>
       </x:c>
       <x:c r="G49" s="9" t="str">
-        <x:v>手动前置；写2，1000ms后写0，再FC01读X7一次。</x:v>
+        <x:v>手动前置；写2→固定200ms→写0；按配置等待（默认1000ms），再单读X7一次。</x:v>
       </x:c>
       <x:c r="H49" s="9" t="str">
         <x:v>MagnetOffAsync
@@ -1883,7 +1883,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R916d64c79e3143bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra52c5a41b5824e71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1933,7 +1933,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="4" t="str">
-        <x:v>充退磁1000ms、其他常规动作200ms、运动触发500ms均为正常完成路径；各动作成功判据按下表区分。</x:v>
+        <x:v>充退磁固定200ms脉冲，清0后等待App.Crane.MagnetFeedbackDelayMs（默认1000ms）；其他常规动作200ms、运动触发500ms。</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -2159,7 +2159,7 @@
         <x:v>手动前置；手动按钮不额外检查X11</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>D4510=2，等1000ms，D4510=0。</x:v>
+        <x:v>D4510=2→200ms→0；配置等待（默认1000ms），再读X6。</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
         <x:v>单次FC01读取X6（63494）。</x:v>
@@ -2179,7 +2179,7 @@
         <x:v>手动前置</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str">
-        <x:v>D4511=2，等1000ms，D4511=0。</x:v>
+        <x:v>D4511=2→200ms→0；配置等待（默认1000ms），再读X7。</x:v>
       </x:c>
       <x:c r="D17" s="9" t="str">
         <x:v>单次FC01读取X7（63495）。</x:v>
@@ -2494,7 +2494,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re73a555e4c7a41de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb38e99a61e7342bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2740,7 +2740,7 @@
         <x:v>正常与异常路径</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
-        <x:v>充退磁1000ms、其他常规动作200ms脉冲描述正常路径；普通动作无运动方法相同的finally复位。运动方法finally尽力把参加轴D4520/21/22清0，清0不等于急停。</x:v>
+        <x:v>充退磁脉冲固定200ms；清0后按App.Crane.MagnetFeedbackDelayMs等待再单读反馈，默认1000ms，参数页天车可编辑。每次动作开始取配置；0不额外等待，负数拒绝。其他常规动作200ms、运动500ms；脉冲描述正常路径，普通动作没有运动方法的finally复位。</x:v>
       </x:c>
       <x:c r="D19" s="9" t="str">
         <x:v>PulseAsync / HomeAsync / MoveAsync</x:v>
@@ -2894,8 +2894,8 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0839a4a7d30d40ee"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0467c83bd09a43d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47db886b875a40d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6731897ff544a1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Docs/设备寄存器地址/天车寄存器地址表.xlsx
+++ b/Docs/设备寄存器地址/天车寄存器地址表.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地址总表" sheetId="1" r:id="R74863d87ab4b422a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作时序" sheetId="2" r:id="R5edaac139932411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通信与接口" sheetId="3" r:id="Rde8d9bfc2b67420d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地址总表" sheetId="1" r:id="R425361a9069c4ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作时序" sheetId="2" r:id="R0c865d968b324e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通信与接口" sheetId="3" r:id="R5a28902ce7344c01"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,7 +52,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -69,6 +69,11 @@
         <x:fgColor rgb="FF776044"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF284B70"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -82,7 +87,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -124,6 +129,12 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -149,6 +160,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="CraneMotionBusy" displayName="CraneMotionBusy" ref="A58:H61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="分类"/>
+    <x:tableColumn id="2" name="PLC地址"/>
+    <x:tableColumn id="3" name="PDU起址"/>
+    <x:tableColumn id="4" name="占用 / 类型"/>
+    <x:tableColumn id="5" name="读写 / 功能码"/>
+    <x:tableColumn id="6" name="信号或参数"/>
+    <x:tableColumn id="7" name="读写值及处理"/>
+    <x:tableColumn id="8" name="源码方法"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CraneActions" displayName="CraneActions" ref="A6:F32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A6:F32"/>
   <x:tableColumns count="6">
@@ -163,7 +190,7 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CraneProtocol" displayName="CraneProtocol" ref="A6:D21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A6:D21"/>
   <x:tableColumns count="4">
@@ -176,7 +203,7 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CraneLegacy" displayName="CraneLegacy" ref="A26:D33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="当前状态"/>
@@ -420,7 +447,7 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>核对日期：2026-10-17；按当前源码实际调用整理，PDU地址均为零基地址。</x:v>
+        <x:v>核对日期：2026-10-19；按当前源码实际调用整理，PDU地址均为零基地址。</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -444,7 +471,7 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="4" t="str">
-        <x:v>共50项当前业务读写点；旧点动接口和未使用常量见“通信与接口”。</x:v>
+        <x:v>共53项当前业务读写点；新增Busy点见下方补充表。旧点动接口见“通信与接口”。</x:v>
       </x:c>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2"/>
@@ -1880,10 +1907,115 @@
 CraneService.cs:618</x:v>
       </x:c>
     </x:row>
+    <x:row r="58" ht="32" customHeight="1">
+      <x:c r="A58" s="18" t="str">
+        <x:v>分类</x:v>
+      </x:c>
+      <x:c r="B58" s="18" t="str">
+        <x:v>PLC地址</x:v>
+      </x:c>
+      <x:c r="C58" s="18" t="str">
+        <x:v>PDU起址</x:v>
+      </x:c>
+      <x:c r="D58" s="18" t="str">
+        <x:v>占用 / 类型</x:v>
+      </x:c>
+      <x:c r="E58" s="18" t="str">
+        <x:v>读写 / 功能码</x:v>
+      </x:c>
+      <x:c r="F58" s="18" t="str">
+        <x:v>信号或参数</x:v>
+      </x:c>
+      <x:c r="G58" s="18" t="str">
+        <x:v>读写值及处理</x:v>
+      </x:c>
+      <x:c r="H58" s="18" t="str">
+        <x:v>源码方法</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="95" customHeight="1">
+      <x:c r="A59" s="9" t="str">
+        <x:v>运动反馈</x:v>
+      </x:c>
+      <x:c r="B59" s="9" t="str">
+        <x:v>B531</x:v>
+      </x:c>
+      <x:c r="C59" s="9" t="n">
+        <x:v>12819</x:v>
+      </x:c>
+      <x:c r="D59" s="9" t="str">
+        <x:v>1 bit</x:v>
+      </x:c>
+      <x:c r="E59" s="9" t="str">
+        <x:v>读 FC01</x:v>
+      </x:c>
+      <x:c r="F59" s="9" t="str">
+        <x:v>X轴运动中 Busy</x:v>
+      </x:c>
+      <x:c r="G59" s="9" t="str">
+        <x:v>参与本阶段时实时读取；位置误差≤配置容差（默认30mm）且Busy=0才普通到位；读失败不当0。 后台也采集供手动页显示，未知不当停止；运动判定仍现读。</x:v>
+      </x:c>
+      <x:c r="H59" s="9" t="str">
+        <x:v>PollAxesAsync</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="95" customHeight="1">
+      <x:c r="A60" s="9" t="str">
+        <x:v>运动反馈</x:v>
+      </x:c>
+      <x:c r="B60" s="9" t="str">
+        <x:v>B536</x:v>
+      </x:c>
+      <x:c r="C60" s="9" t="n">
+        <x:v>12824</x:v>
+      </x:c>
+      <x:c r="D60" s="9" t="str">
+        <x:v>1 bit</x:v>
+      </x:c>
+      <x:c r="E60" s="9" t="str">
+        <x:v>读 FC01</x:v>
+      </x:c>
+      <x:c r="F60" s="9" t="str">
+        <x:v>Y轴运动中 Busy</x:v>
+      </x:c>
+      <x:c r="G60" s="9" t="str">
+        <x:v>参与本阶段时实时读取；位置误差≤配置容差（默认30mm）且Busy=0才普通到位；未参与不读取。 后台也采集供手动页显示，未知不当停止；运动判定仍现读。</x:v>
+      </x:c>
+      <x:c r="H60" s="9" t="str">
+        <x:v>PollAxesAsync</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="95" customHeight="1">
+      <x:c r="A61" s="9" t="str">
+        <x:v>运动反馈</x:v>
+      </x:c>
+      <x:c r="B61" s="9" t="str">
+        <x:v>B541</x:v>
+      </x:c>
+      <x:c r="C61" s="9" t="n">
+        <x:v>12829</x:v>
+      </x:c>
+      <x:c r="D61" s="9" t="str">
+        <x:v>1 bit</x:v>
+      </x:c>
+      <x:c r="E61" s="9" t="str">
+        <x:v>读 FC01</x:v>
+      </x:c>
+      <x:c r="F61" s="9" t="str">
+        <x:v>Z轴运动中 Busy</x:v>
+      </x:c>
+      <x:c r="G61" s="9" t="str">
+        <x:v>参与本阶段时实时读取；位置误差≤配置容差（默认30mm）且Busy=0才普通到位；X2特殊下压规则保留。 后台也采集供手动页显示，未知不当停止；运动判定仍现读。</x:v>
+      </x:c>
+      <x:c r="H61" s="9" t="str">
+        <x:v>PollAxesAsync</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra52c5a41b5824e71"/>
+  <x:tableParts count="2">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd52e625679e24398"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd63082a7a0914624"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1982,7 +2114,7 @@
         <x:v>换算值=目标编码器−当前编码器+当前显示值；FC16分别写D3102/04/06，各占2 Word；对应D4522/21/20写2，500ms后写0。</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>轮询编码器；普通误差≤配置容差，默认5mm；下降阶段监视X2。</x:v>
+        <x:v>轮询编码器；参与轴误差≤配置容差（默认30mm）且Busy=0；下降阶段仍监视X2。</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
         <x:v>InPosition或PressureReached成功；超时、通信失败等返回失败；finally尽力复位参加轴触发位。</x:v>
@@ -2002,7 +2134,7 @@
         <x:v>传入X轴正步长，其余两轴为0；目标=当前显示值+增量；写对应D3102/04/06并触发D4522/21/20，2保持500ms后0。</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>轮询显示坐标；非参加轴跳过；Z正向为下降、负向为上升。</x:v>
+        <x:v>轮询显示值；参与轴误差≤配置容差（默认30mm）且Busy=0；未参与轴不读Busy。Z正向下降、负向上升。</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
         <x:v>每次点击完成一次相对移动；六按钮共用异步命令；当前页面不调用D4501～D4505点动。</x:v>
@@ -2022,7 +2154,7 @@
         <x:v>传入X轴负步长，其余两轴为0；目标=当前显示值+增量；写对应D3102/04/06并触发D4522/21/20，2保持500ms后0。</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>轮询显示坐标；非参加轴跳过；Z正向为下降、负向为上升。</x:v>
+        <x:v>轮询显示值；参与轴误差≤配置容差（默认30mm）且Busy=0；未参与轴不读Busy。Z正向下降、负向上升。</x:v>
       </x:c>
       <x:c r="E9" s="9" t="str">
         <x:v>每次点击完成一次相对移动；六按钮共用异步命令；当前页面不调用D4501～D4505点动。</x:v>
@@ -2042,7 +2174,7 @@
         <x:v>传入Y轴正步长，其余两轴为0；目标=当前显示值+增量；写对应D3102/04/06并触发D4522/21/20，2保持500ms后0。</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>轮询显示坐标；非参加轴跳过；Z正向为下降、负向为上升。</x:v>
+        <x:v>轮询显示值；参与轴误差≤配置容差（默认30mm）且Busy=0；未参与轴不读Busy。Z正向下降、负向上升。</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
         <x:v>每次点击完成一次相对移动；六按钮共用异步命令；当前页面不调用D4501～D4505点动。</x:v>
@@ -2062,7 +2194,7 @@
         <x:v>传入Y轴负步长，其余两轴为0；目标=当前显示值+增量；写对应D3102/04/06并触发D4522/21/20，2保持500ms后0。</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>轮询显示坐标；非参加轴跳过；Z正向为下降、负向为上升。</x:v>
+        <x:v>轮询显示值；参与轴误差≤配置容差（默认30mm）且Busy=0；未参与轴不读Busy。Z正向下降、负向上升。</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
         <x:v>每次点击完成一次相对移动；六按钮共用异步命令；当前页面不调用D4501～D4505点动。</x:v>
@@ -2082,7 +2214,7 @@
         <x:v>传入Z轴正步长，其余两轴为0；目标=当前显示值+增量；写对应D3102/04/06并触发D4522/21/20，2保持500ms后0。</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>轮询显示坐标；非参加轴跳过；Z正向为下降、负向为上升。</x:v>
+        <x:v>轮询显示值；参与轴误差≤配置容差（默认30mm）且Busy=0；未参与轴不读Busy。Z正向下降、负向上升。</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
         <x:v>每次点击完成一次相对移动；六按钮共用异步命令；当前页面不调用D4501～D4505点动。</x:v>
@@ -2102,7 +2234,7 @@
         <x:v>传入Z轴负步长，其余两轴为0；目标=当前显示值+增量；写对应D3102/04/06并触发D4522/21/20，2保持500ms后0。</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
-        <x:v>轮询显示坐标；非参加轴跳过；Z正向为下降、负向为上升。</x:v>
+        <x:v>轮询显示值；参与轴误差≤配置容差（默认30mm）且Busy=0；未参与轴不读Busy。Z正向下降、负向上升。</x:v>
       </x:c>
       <x:c r="E13" s="9" t="str">
         <x:v>每次点击完成一次相对移动；六按钮共用异步命令；当前页面不调用D4501～D4505点动。</x:v>
@@ -2122,7 +2254,7 @@
         <x:v>下降：先XY脉冲及到位，再Z；上升：先Z脉冲及到位，再XY；Z不变：参加轴同阶段脉冲。</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>同阶段为顺序写各轴2，统一等500ms，再顺序写各轴0。</x:v>
+        <x:v>每阶段参与轴须误差≤配置容差（默认30mm）且Busy=0，再触发后续阶段；触发仍写2→500ms→0。</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
         <x:v>各阶段轮询独立计时；默认每次轮询期限60s，不是整个按钮操作总耗时上限。</x:v>
@@ -2494,7 +2626,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb38e99a61e7342bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dc41e88df394fde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2718,7 +2850,7 @@
         <x:v>EnterManualAsync / PressureStopAsync</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="38" customHeight="1">
+    <x:row r="18" ht="106" customHeight="1">
       <x:c r="A18" s="9" t="str">
         <x:v>期限</x:v>
       </x:c>
@@ -2726,7 +2858,7 @@
         <x:v>当前默认</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>客户端通信期限3000ms；运动轮询默认60000ms；普通到位容差默认5mm，下压容差默认15mm。实际运动参数以驱动构造时配置为准。</x:v>
+        <x:v>客户端通信期限3000ms；运动轮询默认60000ms；普通容差默认30mm且参与轴Busy=0，下压容差仍15mm。X/Y/Z Busy（FC01：12819/12824/12829）加入整车后台快照，整轮14次请求；手动页每秒读缓存显示1/0/未知，运动到位仍独立即时读Busy。容差由驱动构造时取值。</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
         <x:v>CraneService / ModbusTcpClient</x:v>
@@ -2894,8 +3026,8 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47db886b875a40d5"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6731897ff544a1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R641bcb0a84c840fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd442c9c1dad4699"/>
   </x:tableParts>
 </x:worksheet>
 </file>